--- a/data/trans_dic/IP2004-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2004-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores a los que les sangran las encías</t>
+          <t>Menores a los que les sangran las encías (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,04</t>
+          <t>0,0; 5,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,08</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,28</t>
+          <t>0,26; 2,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,38</t>
+          <t>0,97; 4,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,99</t>
+          <t>0,0; 2,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,59</t>
+          <t>0,26; 2,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,62</t>
+          <t>0,26; 2,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,4</t>
+          <t>0,94; 5,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,92</t>
+          <t>0,48; 1,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,75</t>
+          <t>0,71; 2,86</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,01</t>
+          <t>0,47; 2,78</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,54</t>
+          <t>2,18; 8,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,31</t>
+          <t>0,85; 5,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 8,24</t>
+          <t>2,77; 7,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,32</t>
+          <t>0,7; 4,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 9,21</t>
+          <t>2,87; 9,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 7,2</t>
+          <t>1,68; 7,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,47</t>
+          <t>1,03; 4,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,84</t>
+          <t>0,89; 4,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 8,02</t>
+          <t>3,31; 7,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,13</t>
+          <t>1,7; 5,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,18</t>
+          <t>2,15; 5,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,7</t>
+          <t>1,06; 3,74</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,25; 10,25</t>
+          <t>4,26; 10,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 10,74</t>
+          <t>4,18; 10,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 7,78</t>
+          <t>2,25; 8,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,55</t>
+          <t>0,6; 3,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 8,61</t>
+          <t>3,16; 8,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,63; 8,36</t>
+          <t>2,61; 8,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 7,36</t>
+          <t>2,0; 7,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,68</t>
+          <t>1,22; 4,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 8,32</t>
+          <t>4,32; 8,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 8,22</t>
+          <t>4,0; 8,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,73</t>
+          <t>2,74; 6,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,34</t>
+          <t>1,24; 3,37</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,76</t>
+          <t>2,41; 4,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,4</t>
+          <t>2,1; 4,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,05</t>
+          <t>1,89; 4,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,19</t>
+          <t>0,61; 2,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,35</t>
+          <t>2,21; 4,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,72</t>
+          <t>1,55; 3,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,5</t>
+          <t>0,94; 2,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,43</t>
+          <t>1,46; 3,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 4,1</t>
+          <t>2,59; 4,15</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,63</t>
+          <t>2,05; 3,59</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,94</t>
+          <t>1,61; 2,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,53</t>
+          <t>1,22; 2,48</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores a los que les sangran las encías (tasa de respuesta: 99,68%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3600</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2994</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2416</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5208</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1934</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2643</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2595</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4571</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>5059</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7803</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1934</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>4571</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>646; 6706</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2281; 10152</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5986</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>648; 5970</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>701; 6919</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1710; 9544</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2433; 9249</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>3582; 14437</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6947</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1601; 9466</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>6017</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3984</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8893</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3242</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>7626</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>6047</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4147</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>4885</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>13643</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>10031</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>13040</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>8127</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2787; 10965</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1336; 7977</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5231; 14950</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1210; 8092</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3985; 13093</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2663; 11204</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1937; 9090</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1881; 10191</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>8823; 20476</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>5344; 16880</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>8122; 20280</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4071; 14412</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>13021</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11763</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7765</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4408</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>11279</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8477</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7601</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>24300</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>20241</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>15066</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>12009</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>8242; 19571</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7140; 18612</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3869; 13773</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1653; 10004</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>6452; 16921</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4686; 14685</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3484; 13190</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>3724; 13791</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>17199; 33104</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>14000; 28884</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>9485; 22727</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>7212; 19555</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>22051</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20955</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18592</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7651</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>21548</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>17120</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>11449</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>17057</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>43599</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>38075</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>30040</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>24707</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>15475; 30453</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>13929; 29559</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>12479; 26752</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>3971; 14928</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>15049; 29460</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>10853; 25767</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6607; 17323</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>10934; 26191</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>34325; 54994</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>28013; 48995</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>21945; 40238</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>17140; 34804</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2004-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2004-Edad-trans_dic.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,09</t>
+          <t>0,0; 4,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,67</t>
+          <t>0,26; 2,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,3</t>
+          <t>0,96; 4,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,85</t>
+          <t>0,0; 3,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,36</t>
+          <t>0,26; 2,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,58</t>
+          <t>0,26; 2,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,26</t>
+          <t>1,0; 5,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,83</t>
+          <t>0,47; 1,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,86</t>
+          <t>0,75; 2,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,78</t>
+          <t>0,52; 2,93</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 8,6</t>
+          <t>2,27; 8,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,1</t>
+          <t>0,86; 5,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,91</t>
+          <t>2,58; 7,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,68</t>
+          <t>0,59; 5,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 9,43</t>
+          <t>3,01; 9,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 7,07</t>
+          <t>1,72; 7,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,82</t>
+          <t>0,75; 4,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,8</t>
+          <t>0,97; 4,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 7,69</t>
+          <t>3,45; 7,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,36</t>
+          <t>1,72; 5,11</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,37</t>
+          <t>2,13; 5,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,74</t>
+          <t>1,11; 3,63</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 10,12</t>
+          <t>4,09; 10,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,18; 10,9</t>
+          <t>3,91; 10,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 8,01</t>
+          <t>2,3; 7,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,63</t>
+          <t>0,6; 3,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 8,28</t>
+          <t>3,23; 8,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 8,19</t>
+          <t>2,44; 8,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 7,58</t>
+          <t>2,03; 7,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,51</t>
+          <t>1,16; 4,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 8,32</t>
+          <t>4,42; 8,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,0; 8,25</t>
+          <t>3,98; 8,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,74; 6,57</t>
+          <t>2,77; 6,58</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,37</t>
+          <t>1,17; 3,3</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,73</t>
+          <t>2,34; 4,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,46</t>
+          <t>2,2; 4,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,06</t>
+          <t>1,91; 4,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,28</t>
+          <t>0,61; 2,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,33</t>
+          <t>2,25; 4,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,67</t>
+          <t>1,52; 3,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,47</t>
+          <t>0,97; 2,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,5</t>
+          <t>1,44; 3,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,15</t>
+          <t>2,64; 4,17</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,59</t>
+          <t>2,07; 3,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,96</t>
+          <t>1,66; 2,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,48</t>
+          <t>1,15; 2,55</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3600</t>
+          <t>0; 2970</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2994</t>
+          <t>0; 2644</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>646; 6706</t>
+          <t>665; 6282</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2281; 10152</t>
+          <t>2269; 10824</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5986</t>
+          <t>0; 6891</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>648; 5970</t>
+          <t>649; 6051</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>701; 6919</t>
+          <t>706; 7223</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1888,27 +1888,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1710; 9544</t>
+          <t>1812; 9730</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2433; 9249</t>
+          <t>2377; 9759</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3582; 14437</t>
+          <t>3777; 14189</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 6947</t>
+          <t>0; 6445</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1601; 9466</t>
+          <t>1759; 9989</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2787; 10965</t>
+          <t>2893; 11275</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1336; 7977</t>
+          <t>1351; 8571</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5231; 14950</t>
+          <t>4878; 14598</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1210; 8092</t>
+          <t>1016; 8763</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3985; 13093</t>
+          <t>4180; 13385</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2663; 11204</t>
+          <t>2730; 12326</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1937; 9090</t>
+          <t>1410; 8333</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1881; 10191</t>
+          <t>2064; 9982</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8823; 20476</t>
+          <t>9182; 20353</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5344; 16880</t>
+          <t>5407; 16082</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8122; 20280</t>
+          <t>8042; 20415</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4071; 14412</t>
+          <t>4275; 13985</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8242; 19571</t>
+          <t>7907; 20176</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7140; 18612</t>
+          <t>6669; 18378</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3869; 13773</t>
+          <t>3956; 13093</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1653; 10004</t>
+          <t>1642; 10155</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6452; 16921</t>
+          <t>6606; 17440</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4686; 14685</t>
+          <t>4371; 14898</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3484; 13190</t>
+          <t>3531; 12641</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3724; 13791</t>
+          <t>3557; 14118</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17199; 33104</t>
+          <t>17567; 32895</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14000; 28884</t>
+          <t>13938; 28162</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9485; 22727</t>
+          <t>9575; 22762</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7212; 19555</t>
+          <t>6810; 19198</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15475; 30453</t>
+          <t>15021; 30106</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13929; 29559</t>
+          <t>14564; 29592</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12479; 26752</t>
+          <t>12574; 27149</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3971; 14928</t>
+          <t>4007; 13380</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15049; 29460</t>
+          <t>15282; 29798</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10853; 25767</t>
+          <t>10646; 25644</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6607; 17323</t>
+          <t>6782; 17999</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10934; 26191</t>
+          <t>10765; 25750</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>34325; 54994</t>
+          <t>34895; 55184</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28013; 48995</t>
+          <t>28308; 49648</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21945; 40238</t>
+          <t>22538; 40371</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17140; 34804</t>
+          <t>16155; 35730</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2004-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2004-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,27 +649,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,84%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -737,27 +737,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 5,04</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -789,44 +789,44 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,2%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,92%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1,0%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,5</t>
+          <t>0,26; 2,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,58</t>
+          <t>0,26; 2,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>1,03; 5,93</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,23; 2,28</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,95; 4,38</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,99</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,26; 2,39</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,26; 2,69</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 5,36</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,93</t>
+          <t>0,48; 1,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,81</t>
+          <t>0,75; 2,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,93</t>
+          <t>0,49; 3,18</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,49%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4,72%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,55%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4,71%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 8,84</t>
+          <t>2,97; 9,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,48</t>
+          <t>1,69; 7,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 7,73</t>
+          <t>0,75; 4,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,06</t>
+          <t>0,88; 4,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 9,64</t>
+          <t>2,29; 8,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 7,77</t>
+          <t>1,22; 5,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,42</t>
+          <t>2,6; 8,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,7</t>
+          <t>0,64; 4,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 7,64</t>
+          <t>3,27; 8,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,11</t>
+          <t>1,78; 5,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,41</t>
+          <t>2,23; 5,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,63</t>
+          <t>0,99; 3,8</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6,73%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6,89%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>4,51%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,09; 10,43</t>
+          <t>3,06; 8,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 10,76</t>
+          <t>2,63; 8,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,61</t>
+          <t>2,09; 7,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,69</t>
+          <t>1,15; 4,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,54</t>
+          <t>4,25; 10,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 8,31</t>
+          <t>4,24; 10,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,26</t>
+          <t>2,22; 7,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,62</t>
+          <t>0,62; 3,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,27</t>
+          <t>4,38; 8,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 8,05</t>
+          <t>3,89; 8,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,58</t>
+          <t>2,73; 6,73</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,3</t>
+          <t>1,25; 3,32</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>3,43%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>3,16%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>2,82%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,68</t>
+          <t>2,24; 4,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,47</t>
+          <t>1,6; 3,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,12</t>
+          <t>1,0; 2,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,04</t>
+          <t>1,51; 3,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,38</t>
+          <t>2,37; 4,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,65</t>
+          <t>2,21; 4,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,57</t>
+          <t>1,87; 4,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,44</t>
+          <t>0,65; 2,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,64; 4,17</t>
+          <t>2,6; 4,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,64</t>
+          <t>2,14; 3,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,97</t>
+          <t>1,57; 2,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,55</t>
+          <t>1,22; 2,6</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,27 +1509,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1577,27 +1577,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>598</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2970</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1665,27 +1665,27 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>0; 3568</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2644</t>
+          <t>0; 3008</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1722,37 +1722,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,44 +1785,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2643</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2595</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4156</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2416</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5208</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1934</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2643</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2595</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>4571</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>5059</t>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>4156</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>665; 6282</t>
+          <t>649; 6544</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2269; 10824</t>
+          <t>701; 7043</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6891</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>1614; 9290</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>575; 5722</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2236; 10353</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6281</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>649; 6051</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>706; 7223</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1812; 9730</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2377; 9759</t>
+          <t>2431; 9676</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3777; 14189</t>
+          <t>3771; 13874</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 6445</t>
+          <t>0; 6361</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1759; 9989</t>
+          <t>1489; 9600</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7626</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6047</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4147</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4659</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>6017</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3984</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>8893</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3242</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>7626</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6047</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4147</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8002</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2893; 11275</t>
+          <t>4127; 12788</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1351; 8571</t>
+          <t>2688; 11425</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4878; 14598</t>
+          <t>1412; 8428</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1016; 8763</t>
+          <t>1757; 9954</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4180; 13385</t>
+          <t>2915; 10894</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2730; 12326</t>
+          <t>1912; 8310</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1410; 8333</t>
+          <t>4903; 15561</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2064; 9982</t>
+          <t>1111; 7929</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9182; 20353</t>
+          <t>8710; 21361</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5407; 16082</t>
+          <t>5601; 16163</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8042; 20415</t>
+          <t>8399; 19567</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4275; 13985</t>
+          <t>3716; 14242</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>11279</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8477</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6812</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>13021</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>11763</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>7765</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4408</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11279</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8477</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7301</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7601</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12009</t>
+          <t>11424</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7907; 20176</t>
+          <t>6245; 17582</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6669; 18378</t>
+          <t>4709; 14989</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3956; 13093</t>
+          <t>3640; 12818</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1642; 10155</t>
+          <t>3369; 12979</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6606; 17440</t>
+          <t>8214; 19822</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4371; 14898</t>
+          <t>7238; 18338</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3531; 12641</t>
+          <t>3821; 13382</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3557; 14118</t>
+          <t>1589; 9907</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17567; 32895</t>
+          <t>17400; 33068</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13938; 28162</t>
+          <t>13632; 28783</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9575; 22762</t>
+          <t>9436; 23276</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6810; 19198</t>
+          <t>6851; 18220</t>
         </is>
       </c>
     </row>
@@ -2346,37 +2346,37 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>21548</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>17120</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>11449</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>15627</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>22051</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>20955</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>18592</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>7651</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>21548</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>17120</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>11449</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17057</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24707</t>
+          <t>23583</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15021; 30106</t>
+          <t>15280; 29635</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14564; 29592</t>
+          <t>11243; 26097</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12574; 27149</t>
+          <t>6984; 17556</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4007; 13380</t>
+          <t>10377; 23077</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15282; 29798</t>
+          <t>15223; 30597</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10646; 25644</t>
+          <t>14641; 29159</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6782; 17999</t>
+          <t>12341; 26686</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10765; 25750</t>
+          <t>4007; 14589</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>34895; 55184</t>
+          <t>34429; 54328</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28308; 49648</t>
+          <t>29207; 49547</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22538; 40371</t>
+          <t>21326; 39957</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16155; 35730</t>
+          <t>15940; 34073</t>
         </is>
       </c>
     </row>
